--- a/data/trans_orig/P33B_R4-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R4-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>124023</t>
+          <t>133018</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106878</t>
+          <t>115141</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142122</t>
+          <t>154595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>264050</t>
+          <t>290761</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>244228</t>
+          <t>267086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286821</t>
+          <t>312596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>388072</t>
+          <t>423779</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>363068</t>
+          <t>395069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>417779</t>
+          <t>451354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>390915</t>
+          <t>445511</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372816</t>
+          <t>423934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408060</t>
+          <t>463388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>488065</t>
+          <t>529399</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465294</t>
+          <t>507564</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>507887</t>
+          <t>553074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>878981</t>
+          <t>974910</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849274</t>
+          <t>947335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>903985</t>
+          <t>1003620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267053</t>
+          <t>1398689</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267053</t>
+          <t>1398689</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267053</t>
+          <t>1398689</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>245540</t>
+          <t>269252</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>237811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288896</t>
+          <t>306177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>373935</t>
+          <t>422228</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>287304</t>
+          <t>387489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>430299</t>
+          <t>456293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>619475</t>
+          <t>691480</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>505846</t>
+          <t>646906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>694134</t>
+          <t>740581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2042741</t>
+          <t>1959254</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1999385</t>
+          <t>1922329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2113910</t>
+          <t>1990695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1863888</t>
+          <t>1749164</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1807524</t>
+          <t>1715099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1950519</t>
+          <t>1783903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3906630</t>
+          <t>3708418</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3831971</t>
+          <t>3659317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4020259</t>
+          <t>3752992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288281</t>
+          <t>2228506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288281</t>
+          <t>2228506</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288281</t>
+          <t>2228506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4526105</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526105</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4526105</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73084</t>
+          <t>84722</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56773</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92246</t>
+          <t>109205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113194</t>
+          <t>125816</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97201</t>
+          <t>108771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130127</t>
+          <t>146801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>186278</t>
+          <t>210538</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162811</t>
+          <t>182986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212027</t>
+          <t>240523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>572570</t>
+          <t>625877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553408</t>
+          <t>601394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>588881</t>
+          <t>642639</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>547269</t>
+          <t>609061</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530336</t>
+          <t>588076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>563262</t>
+          <t>626106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1119839</t>
+          <t>1234939</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1094090</t>
+          <t>1204954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1143306</t>
+          <t>1262491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>442647</t>
+          <t>486992</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>349586</t>
+          <t>442132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>493529</t>
+          <t>531673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>751179</t>
+          <t>838805</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>629153</t>
+          <t>799629</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>825783</t>
+          <t>886762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1193825</t>
+          <t>1325797</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1048625</t>
+          <t>1262872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1292058</t>
+          <t>1388954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3006227</t>
+          <t>3030643</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2955345</t>
+          <t>2985962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3099288</t>
+          <t>3075503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2899222</t>
+          <t>2887624</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2824618</t>
+          <t>2839667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3021248</t>
+          <t>2926800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5905450</t>
+          <t>5918267</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5807217</t>
+          <t>5855110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6050650</t>
+          <t>5981192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>82,57%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448874</t>
+          <t>3517635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448874</t>
+          <t>3517635</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448874</t>
+          <t>3517635</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650401</t>
+          <t>3726429</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650401</t>
+          <t>3726429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650401</t>
+          <t>3726429</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099275</t>
+          <t>7244064</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099275</t>
+          <t>7244064</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099275</t>
+          <t>7244064</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
